--- a/vse-loti/341164463/spec-341164463.xlsx
+++ b/vse-loti/341164463/spec-341164463.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -548,7 +551,7 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" s="4" t="n">
-        <v>1035508.8</v>
+        <v>848777.7</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -577,7 +580,7 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" s="4" t="n">
-        <v>346070.4</v>
+        <v>283664.26</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -606,7 +609,7 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
-        <v>321361.04</v>
+        <v>263410.69</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -635,7 +638,7 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" s="4" t="n">
-        <v>43562.88</v>
+        <v>35707.28</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -664,7 +667,7 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" s="4" t="n">
-        <v>11619.36</v>
+        <v>9524.07</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -693,7 +696,7 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" s="4" t="n">
-        <v>18627.28</v>
+        <v>15268.26</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -724,13 +727,13 @@
         <v>1.992</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>236203.22</v>
+        <v>193609.2</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>118575.91</v>
+        <v>97193.39</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>142291.1</v>
+        <v>118575.94</v>
       </c>
     </row>
     <row r="9">
@@ -743,7 +746,7 @@
         <v>1.992</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>2012952.98</v>
+        <v>1649961.46</v>
       </c>
     </row>
     <row r="10">
@@ -753,21 +756,38 @@
         </is>
       </c>
       <c r="G10" s="8" t="n">
+        <v>1649961.46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22% (справочно):</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>2012952.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; по ч. 1 ст. 22 44-ФЗ цена контракта включает налоги, поэтому сумма документа принята как цена с НДС. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
           <t>Источник: Обоснование НМЦК в соответствии с разделом III Приказа Минэкономразвития России от 02.10.2013 N 567 (2).xlsx</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="A14:B16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341164463/spec-341164463.xlsx
+++ b/vse-loti/341164463/spec-341164463.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -513,17 +514,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -550,11 +556,14 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="4" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
         <v>848777.7</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" s="4" t="n">
+        <v>1035508.79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -579,11 +588,14 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
         <v>283664.26</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" s="4" t="n">
+        <v>346070.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -608,11 +620,14 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
         <v>263410.69</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" s="4" t="n">
+        <v>321361.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -637,11 +652,14 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
         <v>35707.28</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" s="4" t="n">
+        <v>43562.88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -666,11 +684,14 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" s="4" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
         <v>9524.07</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>11619.37</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -695,11 +716,14 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="4" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="4" t="n">
         <v>15268.26</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" s="4" t="n">
+        <v>18627.28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -727,14 +751,17 @@
         <v>1.992</v>
       </c>
       <c r="G8" s="4" t="n">
+        <v>97193.39</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>193609.2</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>97193.39</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>118575.94</v>
       </c>
+      <c r="J8" s="4" t="n">
+        <v>236203.22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -746,7 +773,16 @@
         <v>1.992</v>
       </c>
       <c r="G9" s="8" t="n">
+        <v>828293.91</v>
+      </c>
+      <c r="H9" s="8" t="n">
         <v>1649961.46</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>1010518.57</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>2012952.98</v>
       </c>
     </row>
     <row r="10">
@@ -755,7 +791,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="H10" s="8" t="n">
         <v>1649961.46</v>
       </c>
     </row>
@@ -765,7 +801,7 @@
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="J11" s="8" t="n">
         <v>2012952.98</v>
       </c>
     </row>
